--- a/dados/coletas/coleta_2026-10-12.xlsx
+++ b/dados/coletas/coleta_2026-10-12.xlsx
@@ -10,7 +10,7 @@
     <sheet name="coleta" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'coleta'!$A$1:$H$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'coleta'!$A$1:$I$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,17 +433,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,37 +455,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>loja</t>
+          <t>nome_loja</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>url_base</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nome_produto</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>categoria_produto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>nome_produto</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>preco</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>url_oferta</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>titulo_anuncio</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>preco</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>preco_prazo</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>url_oferta</t>
         </is>
       </c>
     </row>
@@ -494,34 +500,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 5600</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 5600, 3.5GHz (4.4GHz Turbo), AM4 - 100-100000927BOX</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>827.9</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/355263/processador-amd-ryzen-5-5600-3-5ghz-4-4ghz-turbo-am4-100-100000927box</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 5600, 3.5GHz (4.4GHz Turbo), AM4 - 100-100000927BOX</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>919.89</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/355263/processador-amd-ryzen-5-5600-3-5ghz-4-4ghz-turbo-am4-100-100000927box</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -530,34 +541,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 5700X</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 5700X</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 5700X, 3.4GHz (4.6GHz Max Turbo), Cache 36MB, 8 Núcleos, 16 Threads, AM4, Sem Vídeo Integrado - 100-100000926WOF</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1199.99</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/320797/processador-amd-ryzen-7-5700x-3-4ghz-4-6ghz-max-turbo-cache-36mb-8-nucleos-16-threads-am4-sem-video-integrado-100-100000926wof</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 5700X, 3.4GHz (4.6GHz Max Turbo), Cache 36MB, 8 Núcleos, 16 Threads, AM4, Sem Vídeo Integrado - 100-100000926WOF</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>2686.16</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/320797/processador-amd-ryzen-7-5700x-3-4ghz-4-6ghz-max-turbo-cache-36mb-8-nucleos-16-threads-am4-sem-video-integrado-100-100000926wof</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -566,34 +582,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 7600</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 7600, 3.8GHz (5.1GHz Max Turbo), Cache 38MB, 6 Núcleos, 12 Threads, AM5, Com Vídeo Integrado - 100-100001015BOX</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>999.99</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/405799/processador-amd-ryzen-5-7600-3-8ghz-5-1ghz-max-turbo-cache-38mb-6-nucleos-12-threads-am5-com-video-integrado-100-100001015box</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 7600, 3.8GHz (5.1GHz Max Turbo), Cache 38MB, 6 Núcleos, 12 Threads, AM5, Com Vídeo Integrado - 100-100001015BOX</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>1823.52</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/405799/processador-amd-ryzen-5-7600-3-8ghz-5-1ghz-max-turbo-cache-38mb-6-nucleos-12-threads-am5-com-video-integrado-100-100001015box</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -602,34 +623,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 7800X3D</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 7800x3d, 4.2GHz, 5.0GHz Max Turbo, Cache 104MB, Am5, C/ Vídeo E Sem Cooler - 100-100000910wof</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1978.9</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/466557/processador-amd-ryzen-7-7800x3d-4-2ghz-5-0ghz-max-turbo-cache-104mb-am5-c-video-e-sem-cooler-100-100000910wof</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 7800x3d, 4.2GHz, 5.0GHz Max Turbo, Cache 104MB, Am5, C/ Vídeo E Sem Cooler - 100-100000910wof</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>2264.19</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/466557/processador-amd-ryzen-7-7800x3d-4-2ghz-5-0ghz-max-turbo-cache-104mb-am5-c-video-e-sem-cooler-100-100000910wof</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -638,34 +664,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-12400F</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-12400F, 2.5GHz (4.4GHz Max Turbo), Cache 18MB, 6 Núcleos, 12 Threads, LGA 1700, Sem Vídeo Integrado - BX8071512400F</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>899.99</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/283718/processador-intel-core-i5-12400f-2-5ghz-4-4ghz-max-turbo-cache-18mb-6-nucleos-12-threads-lga-1700-sem-video-integrado-bx8071512400f</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-12400F, 2.5GHz (4.4GHz Max Turbo), Cache 18MB, 6 Núcleos, 12 Threads, LGA 1700, Sem Vídeo Integrado - BX8071512400F</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>1658.32</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/283718/processador-intel-core-i5-12400f-2-5ghz-4-4ghz-max-turbo-cache-18mb-6-nucleos-12-threads-lga-1700-sem-video-integrado-bx8071512400f</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -674,34 +705,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-14400F</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Processador Intel Core I5 14400f 14ª Geração, 3.5 Ghz (4.7 Ghz Turbo), Cache 20mb, 10 Núcleos, 16 Threads, Lga1700, S/ Vídeo Integrado - Bx8071514400f</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1069.99</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/531209/processador-intel-core-i5-14400f-14-geracao-3-5-ghz-4-7-ghz-turbo-cache-20mb-10-nucleos-16-threads-lga1700-sem-video-integrado-bx8071514400f</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Processador Intel Core I5 14400f 14ª Geração, 3.5 Ghz (4.7 Ghz Turbo), Cache 20mb, 10 Núcleos, 16 Threads, Lga1700, S/ Vídeo Integrado - Bx8071514400f</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>1189.99</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/531209/processador-intel-core-i5-14400f-14-geracao-3-5-ghz-4-7-ghz-turbo-cache-20mb-10-nucleos-16-threads-lga1700-sem-video-integrado-bx8071514400f</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -710,34 +746,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 5060 8GB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 5060 8GB</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Placa de Video Palit GeForce RTX 5060 8GB INFINITY 2 OC GDDR7 128bits - NE75060V19P1-GB2063L</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2799.99</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/988706/placa-de-video-palit-geforce-rtx-5060-8gb-infinity-2-oc-gddr7-128bits-ne75060v19p1-gb2063l</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Placa de Video Palit GeForce RTX 5060 8GB INFINITY 2 OC GDDR7 128bits - NE75060V19P1-GB2063L</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>3823.98</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/988706/placa-de-video-palit-geforce-rtx-5060-8gb-infinity-2-oc-gddr7-128bits-ne75060v19p1-gb2063l</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -746,34 +787,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 5070 12GB</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 5070 12GB</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Placa de Video Palit GeForce RTX 5070 WHITE OC 12GB GDDR7 192bit 3-DP e HDMI - NE75070U19K9-GB2050W</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>5299.99</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/989622/placa-de-video-palit-geforce-rtx-5070-white-oc-12gb-gddr7-192bit-3-dp-e-hdmi-ne75070u19k9-gb2050w</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Placa de Video Palit GeForce RTX 5070 WHITE OC 12GB GDDR7 192bit 3-DP e HDMI - NE75070U19K9-GB2050W</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>6666.66</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/989622/placa-de-video-palit-geforce-rtx-5070-white-oc-12gb-gddr7-192bit-3-dp-e-hdmi-ne75070u19k9-gb2050w</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -782,34 +828,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 3060 12GB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 3060 12GB</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Placa De Vídeo Husky Alpha RTX 3060, Nvidia, 12GB, GDDR6, 192-Bit, Dual Fan, HDMI, 3x DisplayPort - HVG023060</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2199.99</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/996572/placa-de-video-husky-alpha-rtx-3060-nvidia-12gb-gddr6-192-bit-dual-fan-hdmi-3x-displayport-hvg023060</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Placa De Vídeo Husky Alpha RTX 3060, Nvidia, 12GB, GDDR6, 192-Bit, Dual Fan, HDMI, 3x DisplayPort - HVG023060</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>3529.4</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/996572/placa-de-video-husky-alpha-rtx-3060-nvidia-12gb-gddr6-192-bit-dual-fan-hdmi-3x-displayport-hvg023060</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -818,34 +869,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo Radeon RX 7600 8GB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo Radeon RX 7600 8GB</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo RX 7600 Challenger ASRock AMD Radeon,  8GB GDDR6 - 90-GA41ZZ-00UANF</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1909.99</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/459144/placa-de-video-rx-7600-challenger-asrock-amd-radeon-8gb-gddr6-90-ga41zz-00uanf</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo RX 7600 Challenger ASRock AMD Radeon,  8GB GDDR6 - 90-GA41ZZ-00UANF</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>2823.52</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/459144/placa-de-video-rx-7600-challenger-asrock-amd-radeon-8gb-gddr6-90-ga41zz-00uanf</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -854,34 +910,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 8GB DDR4 3200MHz</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 8GB DDR4 3200MHz</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Memória RAM Kingston Fury Beast, 8GB, 3200MHz, DDR4, CL16, Preto - KF432C16BB/8</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>669.99</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/172365/memoria-ram-kingston-fury-beast-8gb-3200mhz-ddr4-cl16-preto-kf432c16bb-8</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Memória RAM Kingston Fury Beast, 8GB, 3200MHz, DDR4, CL16, Preto - KF432C16BB/8</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>952.74</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/172365/memoria-ram-kingston-fury-beast-8gb-3200mhz-ddr4-cl16-preto-kf432c16bb-8</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -890,34 +951,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 16GB DDR4 3200MHz</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 16GB DDR4 3200MHz</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Memória Ram Kingston Hyperx Fury Beast Ddr4 16gb 3200mhz Cl16 Udimm – Desktop</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>999.3099999999999</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/938663/memoria-ram-kingston-hyperx-ddr4-16gb-2666mhz-cl16-udimm-desktop</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Memória Ram Kingston Hyperx Fury Beast Ddr4 16gb 3200mhz Cl16 Udimm – Desktop</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>1051.9</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/938663/memoria-ram-kingston-hyperx-ddr4-16gb-2666mhz-cl16-udimm-desktop</t>
-        </is>
       </c>
     </row>
     <row r="14">
@@ -926,34 +992,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast, 16GB, 5600MHz, DDR5, CL40, Preto - KF556C40BB-16</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2199</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/349654/memoria-kingston-fury-beast-16gb-5600mhz-ddr5-cl40-preto-kf556c40bb-16</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast, 16GB, 5600MHz, DDR5, CL40, Preto - KF556C40BB-16</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>2199</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/349654/memoria-kingston-fury-beast-16gb-5600mhz-ddr5-cl40-preto-kf556c40bb-16</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -962,34 +1033,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SSD Kingston NV3 1TB M.2 NVMe</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>SSD Kingston NV3 1TB M.2 NVMe</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SSD Kingston 1TB Nv3 M.2 Nvme PCIe 4, Leitura 6000MB/s, Gravação 4000MB/s, Ultra Rápido - Snv3s/1000g</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1032.13</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/633107/ssd-kingston-1tb-padrao-nv3-m-2-2280-nvme-4-0-gen-4x4-leitura-6000-e-gravacao-4000mbps-ultra-rapido-snv3s-1000g</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SSD Kingston 1TB Nv3 M.2 Nvme PCIe 4, Leitura 6000MB/s, Gravação 4000MB/s, Ultra Rápido - Snv3s/1000g</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>1146.81</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/633107/ssd-kingston-1tb-padrao-nv3-m-2-2280-nvme-4-0-gen-4x4-leitura-6000-e-gravacao-4000mbps-ultra-rapido-snv3s-1000g</t>
-        </is>
       </c>
     </row>
     <row r="16">
@@ -998,34 +1074,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SSD Samsung 990 Pro 1TB M.2 NVMe</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>SSD Samsung 990 Pro 1TB M.2 NVMe</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>SSD Samsung 990 Pro 1TB, Nvme M.2 2280, Mz-v9p1t0b/am.</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>2399</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/464267/ssd-samsung-990-pro-1tb-nvme-m-2-2280-mz-v9p1t0b-am-</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SSD Samsung 990 Pro 1TB, Nvme M.2 2280, Mz-v9p1t0b/am.</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>2399</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/464267/ssd-samsung-990-pro-1tb-nvme-m-2-2280-mz-v9p1t0b-am-</t>
-        </is>
       </c>
     </row>
     <row r="17">
@@ -1034,34 +1115,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SSD Kingston A400 480GB SATA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>SSD Kingston A400 480GB SATA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>SSD Kingston A400, 480GB, Sata Iii, 2.5", Leitura: 500mb/s, Gravação: 450mb/s, Preto - Sa400s37/480g</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>466.39</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/781777/ssd-kingston-a400-480gb-sata-iii-2-5-leitura-500mb-s-gravacao-450mb-s-preto-sa400s37-480g</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SSD Kingston A400, 480GB, Sata Iii, 2.5", Leitura: 500mb/s, Gravação: 450mb/s, Preto - Sa400s37/480g</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>529.99</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/781777/ssd-kingston-a400-480gb-sata-iii-2-5-leitura-500mb-s-gravacao-450mb-s-preto-sa400s37-480g</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -1070,34 +1156,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Placa-mãe ASUS TUF Gaming B550M-Plus</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Placa-mãe</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Placa-mãe ASUS TUF Gaming B550M-Plus</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Placa-Mãe Asus TUF Gaming B550M-PLUS, AMD AM4, mATX , DDR4, M.2, Aura para fita RGB - 90MB14A0-C1BAY0</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>741.9</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/172706/placa-mae-asus-tuf-gaming-b550m-plus-amd-am4-matx-ddr4-m-2-aura-para-fita-rgb-90mb14a0-c1bay0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Placa-Mãe Asus TUF Gaming B550M-PLUS, AMD AM4, mATX , DDR4, M.2, Aura para fita RGB - 90MB14A0-C1BAY0</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>824.33</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/172706/placa-mae-asus-tuf-gaming-b550m-plus-amd-am4-matx-ddr4-m-2-aura-para-fita-rgb-90mb14a0-c1bay0</t>
-        </is>
       </c>
     </row>
     <row r="19">
@@ -1106,34 +1197,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Placa-mãe MSI PRO B650M-P</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Placa-mãe</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Placa-mãe MSI PRO B650M-P</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Placa Mãe Msi Pro B650m-p, Matx Am5 Ddr5 HDMI, Displayport Vga M.2 Usb 3.2</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>994.38</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/532385/placa-mae-msi-pro-b650m-p-matx-am5-ddr5-hdmi-displayport-vga-m-2-usb-3-2</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Placa Mãe Msi Pro B650m-p, Matx Am5 Ddr5 HDMI, Displayport Vga M.2 Usb 3.2</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>1057.85</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/532385/placa-mae-msi-pro-b650m-p-matx-am5-ddr5-hdmi-displayport-vga-m-2-usb-3-2</t>
-        </is>
       </c>
     </row>
     <row r="20">
@@ -1142,34 +1238,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fonte Corsair CX650 650W 80 Plus Bronze</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Fonte Corsair CX650 650W 80 Plus Bronze</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Fonte Corsair CX Series CX650, 650W, 80 Plus Bronze, Com Cabo, Preto - CP-9020278-BR</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>359.99</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/516056/fonte-corsair-cx-series-cx650-650w-80-plus-bronze-com-cabo-preto-cp-9020278-br</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Fonte Corsair CX Series CX650, 650W, 80 Plus Bronze, Com Cabo, Preto - CP-9020278-BR</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>433.32</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/516056/fonte-corsair-cx-series-cx650-650w-80-plus-bronze-com-cabo-preto-cp-9020278-br</t>
-        </is>
       </c>
     </row>
     <row r="21">
@@ -1178,34 +1279,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fonte MSI MAG A650BN 650W 80 Plus Bronze</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Fonte MSI MAG A650BN 650W 80 Plus Bronze</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Fonte MSI MAG A650BN, 650W, 80 Plus Bronze, PFC Ativo, Com Cabo, Preto - 306-7ZP2B22-CE0</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>289.99</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/369658/fonte-msi-mag-a650bn-650w-80-plus-bronze-pfc-ativo-com-cabo-preto-306-7zp2b22-ce0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Fonte MSI MAG A650BN, 650W, 80 Plus Bronze, PFC Ativo, Com Cabo, Preto - 306-7ZP2B22-CE0</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>388.88</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/369658/fonte-msi-mag-a650bn-650w-80-plus-bronze-pfc-ativo-com-cabo-preto-306-7zp2b22-ce0</t>
-        </is>
       </c>
     </row>
     <row r="22">
@@ -1214,34 +1320,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Fonte XPG Core Reactor II VE 750W 80 Plus Gold</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Fonte XPG Core Reactor II VE 750W 80 Plus Gold</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Fonte Xpg Core Reactor Ii Ve, 750w, 80 Plus Gold, Modular, Pfc Ativo, Preta - 75261425</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>753.95</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/1074346/fonte-xpg-core-reactor-ii-ve-750w-80-plus-gold-modular-pfc-ativo-preta-75261425</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Fonte Xpg Core Reactor Ii Ve, 750w, 80 Plus Gold, Modular, Pfc Ativo, Preta - 75261425</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>793.63</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/1074346/fonte-xpg-core-reactor-ii-ve-750w-80-plus-gold-modular-pfc-ativo-preta-75261425</t>
-        </is>
       </c>
     </row>
     <row r="23">
@@ -1250,34 +1361,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>pichau</t>
+          <t>Pichau</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>https://www.pichau.com.br</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 5700X</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 5700X</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 5700X, 8-Core, 16-Threads, 3.4GHz (4.6GHz Turbo), Cache 36MB, AM4, 100-100000926WOF</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1199.99</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.pichau.com.br/processador-amd-ryzen-7-5700x-8-core-16-threads-3-4ghz-4-6ghz-turbo-cache-36mb-am4-100-100000926wof</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 5700X, 8-Core, 16-Threads, 3.4GHz (4.6GHz Turbo), Cache 36MB, AM4, 100-100000926WOF</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>1411.75</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>https://www.pichau.com.br/processador-amd-ryzen-7-5700x-8-core-16-threads-3-4ghz-4-6ghz-turbo-cache-36mb-am4-100-100000926wof</t>
-        </is>
       </c>
     </row>
     <row r="24">
@@ -1286,34 +1402,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pichau</t>
+          <t>Pichau</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>https://www.pichau.com.br</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 7800X3D</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 7800X3D, 8-Core, 16-Threads, 4.2GHz (5.0GHzTurbo), Cache 104MB, AM5, 100-100000910WOF</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1999.99</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.pichau.com.br/processador-amd-ryzen-7-7800x3d-8-core-16-threads-4-2ghz-5-0ghzturbo-cache-104mb-am5-100-100000910wof</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 7800X3D, 8-Core, 16-Threads, 4.2GHz (5.0GHzTurbo), Cache 104MB, AM5, 100-100000910WOF</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>2352.93</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>https://www.pichau.com.br/processador-amd-ryzen-7-7800x3d-8-core-16-threads-4-2ghz-5-0ghzturbo-cache-104mb-am5-100-100000910wof</t>
-        </is>
       </c>
     </row>
     <row r="25">
@@ -1322,34 +1443,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>pichau</t>
+          <t>Pichau</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>https://www.pichau.com.br</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-14400F</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-14400F, 10-Core, 16-Threads, 3.5GHz (4.7GHz Turbo), Cache 20MB, LGA1700, BX8071514400F</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>999.99</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.pichau.com.br/processador-intel-core-i5-14400f-10-core-16-threads-3-5ghz-4-7ghz-turbo-cache-20mb-lga1700-bx8071514400f</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-14400F, 10-Core, 16-Threads, 3.5GHz (4.7GHz Turbo), Cache 20MB, LGA1700, BX8071514400F</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>1176.46</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>https://www.pichau.com.br/processador-intel-core-i5-14400f-10-core-16-threads-3-5ghz-4-7ghz-turbo-cache-20mb-lga1700-bx8071514400f</t>
-        </is>
       </c>
     </row>
     <row r="26">
@@ -1358,34 +1484,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>terabyte</t>
+          <t>Terabyte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>https://www.terabyteshop.com.br</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 5700X</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 5700X</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 5700X 3.4GHz (4.6GHz Turbo), 8-Cores 16-Threads, AM4, Sem Cooler, 100-100000926WOF</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1199.99</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/20813/processador-amd-ryzen-7-5700x-34ghz-46ghz-turbo-8-cores-16-threads-am4-sem-cooler-100-100000926wof</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 5700X 3.4GHz (4.6GHz Turbo), 8-Cores 16-Threads, AM4, Sem Cooler, 100-100000926WOF</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>1411.8</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>https://www.terabyteshop.com.br/produto/20813/processador-amd-ryzen-7-5700x-34ghz-46ghz-turbo-8-cores-16-threads-am4-sem-cooler-100-100000926wof</t>
-        </is>
       </c>
     </row>
     <row r="27">
@@ -1394,34 +1525,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>terabyte</t>
+          <t>Terabyte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>https://www.terabyteshop.com.br</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 7600</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 7600, 3.8GHz (5.1GHz Turbo), 6-Cores 12-Threads, AM5, Com Cooler AMD Wraith Stealth, 100-100001015BOX</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1299.99</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/23415/processador-amd-ryzen-5-7600-38ghz-51ghz-turbo-6-cores-12-threads-am5-com-cooler-amd-wraith-stealth-100-100001015box</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 7600, 3.8GHz (5.1GHz Turbo), 6-Cores 12-Threads, AM5, Com Cooler AMD Wraith Stealth, 100-100001015BOX</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>1529.4</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://www.terabyteshop.com.br/produto/23415/processador-amd-ryzen-5-7600-38ghz-51ghz-turbo-6-cores-12-threads-am5-com-cooler-amd-wraith-stealth-100-100001015box</t>
-        </is>
       </c>
     </row>
     <row r="28">
@@ -1430,34 +1566,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>terabyte</t>
+          <t>Terabyte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>https://www.terabyteshop.com.br</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-12400F</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5 12400F, 2.5GHz (4.4GHz Turbo), 12ª Geração, 6-Cores 12-Threads, LGA 1700, Com Cooler, BX8071512400F</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>829.99</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/20072/processador-intel-core-i5-12400f-25ghz-44ghz-turbo-12-geracao-6-cores-12-threads-lga-1700-bx8071512400f</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5 12400F, 2.5GHz (4.4GHz Turbo), 12ª Geração, 6-Cores 12-Threads, LGA 1700, Com Cooler, BX8071512400F</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>976.4400000000001</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>https://www.terabyteshop.com.br/produto/20072/processador-intel-core-i5-12400f-25ghz-44ghz-turbo-12-geracao-6-cores-12-threads-lga-1700-bx8071512400f</t>
-        </is>
       </c>
     </row>
     <row r="29">
@@ -1466,34 +1607,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>terabyte</t>
+          <t>Terabyte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>https://www.terabyteshop.com.br</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-14400F</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5 14400F, 3.5 GHz (4.7GHz Turbo), 14ª Geração, 10-Cores 16-Threads, LGA 1700, BX8071514400F</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>999.99</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/27612/processador-intel-core-i5-14400f-35-ghz-47ghz-turbo-14-geracao-10-cores-16-threads-lga-1700-bx8071514400f</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5 14400F, 3.5 GHz (4.7GHz Turbo), 14ª Geração, 10-Cores 16-Threads, LGA 1700, BX8071514400F</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>1176.48</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>https://www.terabyteshop.com.br/produto/27612/processador-intel-core-i5-14400f-35-ghz-47ghz-turbo-14-geracao-10-cores-16-threads-lga-1700-bx8071514400f</t>
-        </is>
       </c>
     </row>
     <row r="30">
@@ -1502,30 +1648,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 5600</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 5600 AM4 3.5GHz (Sem caixa) – 6 Núcleos 12 Threads – Até 4.4GHz – NoBox</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>835.9</v>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0GKHVP14D</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0GKHVP14D</t>
+          <t>Processador AMD Ryzen 5 5600 AM4 3.5GHz (Sem caixa) – 6 Núcleos 12 Threads – Até 4.4GHz – NoBox</t>
         </is>
       </c>
     </row>
@@ -1535,30 +1686,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 5700X</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 5700X</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 5700X, 3,4 GHz, 8 núcleos, 16 threads, cache de 32 MB, soquete AM4, OEM</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>987.05</v>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0C3T4MFMM</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0C3T4MFMM</t>
+          <t>Processador AMD Ryzen 7 5700X, 3,4 GHz, 8 núcleos, 16 threads, cache de 32 MB, soquete AM4, OEM</t>
         </is>
       </c>
     </row>
@@ -1568,30 +1724,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 7600</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>PROCESSADOR AMD RYZEN 5 7600 4.0GHz (TURBO 5.2GHz) 38MB CACHE AM5 100-100001015BOX</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>999.99</v>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0BMQJWBDM</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0BMQJWBDM</t>
+          <t>PROCESSADOR AMD RYZEN 5 7600 4.0GHz (TURBO 5.2GHz) 38MB CACHE AM5 100-100001015BOX</t>
         </is>
       </c>
     </row>
@@ -1601,30 +1762,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 7800X3D</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AMD Ryzen 7 7800X3D 8 x 4,2GHz Octa Core Processador (CPU) Bandeja Socket (PC): AM5 120W</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1895.89</v>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0CTD76W9C</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0CTD76W9C</t>
+          <t>AMD Ryzen 7 7800X3D 8 x 4,2GHz Octa Core Processador (CPU) Bandeja Socket (PC): AM5 120W</t>
         </is>
       </c>
     </row>
@@ -1634,30 +1800,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-12400F</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>PROCESSADOR INTEL CORE I5-12400F 2.5GHz (TURBO 4.4GHz) 18MB CACHE LGA1700 12° GERACAO BX8071512400F</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1105.17</v>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B09NPJRDGD</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B09NPJRDGD</t>
+          <t>PROCESSADOR INTEL CORE I5-12400F 2.5GHz (TURBO 4.4GHz) 18MB CACHE LGA1700 12° GERACAO BX8071512400F</t>
         </is>
       </c>
     </row>
@@ -1667,30 +1838,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-14400F</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-14400F LGA 1700 BX8071514400F</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1000</v>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0CQ3142LB</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0CQ3142LB</t>
+          <t>Processador Intel Core i5-14400F LGA 1700 BX8071514400F</t>
         </is>
       </c>
     </row>
@@ -1700,30 +1876,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 5060 8GB</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 5060 8GB</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>GAINWARD Placa gráfica RTX 5060 Ghost 8GB GDDR7 128bit 3-DP HDMI NE75060019P1-GB2063B VD9198</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>2799.98</v>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0F8H4RWB8</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0F8H4RWB8</t>
+          <t>GAINWARD Placa gráfica RTX 5060 Ghost 8GB GDDR7 128bit 3-DP HDMI NE75060019P1-GB2063B VD9198</t>
         </is>
       </c>
     </row>
@@ -1733,30 +1914,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 5070 12GB</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 5070 12GB</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Palit RTX5070 Branco OC 12GB GDDR7 NE75070U19K9-GB2050W Retail</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>5594.43</v>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0FQV7G9WY</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0FQV7G9WY</t>
+          <t>Palit RTX5070 Branco OC 12GB GDDR7 NE75070U19K9-GB2050W Retail</t>
         </is>
       </c>
     </row>
@@ -1766,30 +1952,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 3060 12GB</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 3060 12GB</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Placa De Vídeo Husky Alpha RTX 3060, Nvidia, 12GB, GDDR6, 192-Bit, Dual Fan, HDMI, 3x DisplayPort - HVG023060</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>2458.8</v>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0H378SSY3</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0H378SSY3</t>
+          <t>Placa De Vídeo Husky Alpha RTX 3060, Nvidia, 12GB, GDDR6, 192-Bit, Dual Fan, HDMI, 3x DisplayPort - HVG023060</t>
         </is>
       </c>
     </row>
@@ -1799,30 +1990,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo Radeon RX 7600 8GB</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo Radeon RX 7600 8GB</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo ASRock Radeon RX 7600 Challenger OC, 8GB, GDDR6, 128-Bit, FSR, Ray Tracing, Preto</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>2134.69</v>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0C626FFG2</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0C626FFG2</t>
+          <t>Placa de Vídeo ASRock Radeon RX 7600 Challenger OC, 8GB, GDDR6, 128-Bit, FSR, Ray Tracing, Preto</t>
         </is>
       </c>
     </row>
@@ -1832,30 +2028,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 8GB DDR4 3200MHz</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 8GB DDR4 3200MHz</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>MEMÓRIA KINGSTON FURY BEAST DIMM DDR4 8GB 3200 MHZ KF432C16BB/8 1,35V 1Rx* 288 pinos Desktop Gamer</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>451.24</v>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B097K5J1SB</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B097K5J1SB</t>
+          <t>MEMÓRIA KINGSTON FURY BEAST DIMM DDR4 8GB 3200 MHZ KF432C16BB/8 1,35V 1Rx* 288 pinos Desktop Gamer</t>
         </is>
       </c>
     </row>
@@ -1865,30 +2066,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 16GB DDR4 3200MHz</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 16GB DDR4 3200MHz</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>KF432C16BB/16 - Memória de 16GB DIMM DDR4 3200Mhz FURY Beast 1,35V 1Rx8 288 pinos para desktop/gamers, Preto</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>798.1900000000001</v>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B097K3WV9J</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B097K3WV9J</t>
+          <t>KF432C16BB/16 - Memória de 16GB DIMM DDR4 3200Mhz FURY Beast 1,35V 1Rx8 288 pinos para desktop/gamers, Preto</t>
         </is>
       </c>
     </row>
@@ -1898,30 +2104,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Kingston KF556C40BB-16 - Módulo de memória de 16GB DDR5 5600Mhz FURY Beast Black 1,25V 1Rx8 288 pinos para desktop/gamers,NULL</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>2070.99</v>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B09N5WSSQD</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B09N5WSSQD</t>
+          <t>Kingston KF556C40BB-16 - Módulo de memória de 16GB DDR5 5600Mhz FURY Beast Black 1,25V 1Rx8 288 pinos para desktop/gamers,NULL</t>
         </is>
       </c>
     </row>
@@ -1931,30 +2142,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SSD Kingston NV3 1TB M.2 NVMe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>SSD Kingston NV3 1TB M.2 NVMe</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>SSD Kingston NV3 1TB M.2 2280 NVMe Gen4, Desempenho e Eficiência para Upgrade de PC – SNV3S/1000G</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>930.05</v>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0DBR3DZWG</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0DBR3DZWG</t>
+          <t>SSD Kingston NV3 1TB M.2 2280 NVMe Gen4, Desempenho e Eficiência para Upgrade de PC – SNV3S/1000G</t>
         </is>
       </c>
     </row>
@@ -1964,30 +2180,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SSD Samsung 990 Pro 1TB M.2 NVMe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SSD Samsung 990 Pro 1TB M.2 NVMe</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>SSD Samsung 990 PRO 1TB NVMe M.2 2280 (Leitura até 7450MB/s e Gravação até 6900MB/s)</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1702.98</v>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0BHJF2VRN</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0BHJF2VRN</t>
+          <t>SSD Samsung 990 PRO 1TB NVMe M.2 2280 (Leitura até 7450MB/s e Gravação até 6900MB/s)</t>
         </is>
       </c>
     </row>
@@ -1997,30 +2218,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SSD Kingston A400 480GB SATA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SSD Kingston A400 480GB SATA</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Ssd 480Gb Kingston A400 Bulk</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>615.6</v>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B08NG86HZD</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B08NG86HZD</t>
+          <t>Ssd 480Gb Kingston A400 Bulk</t>
         </is>
       </c>
     </row>
@@ -2030,30 +2256,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Placa-mãe MSI PRO B650M-P</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>Placa-mãe</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Placa-mãe MSI PRO B650M-P</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>MSI Placa-mãe PRO B650M-P V1, Micro-ATX - Suporta processadores AMD Ryzen 9000/8000/7000, AM5 - DDR5 Memory Boost 6000+MHz/OC, 1 x PCIe 4.0 x16, 2 x M.2 Gen4, LAN 2.5G</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1371.19</v>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0FBT23ZY8</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0FBT23ZY8</t>
+          <t>MSI Placa-mãe PRO B650M-P V1, Micro-ATX - Suporta processadores AMD Ryzen 9000/8000/7000, AM5 - DDR5 Memory Boost 6000+MHz/OC, 1 x PCIe 4.0 x16, 2 x M.2 Gen4, LAN 2.5G</t>
         </is>
       </c>
     </row>
@@ -2063,30 +2294,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Fonte Corsair CX650 650W 80 Plus Bronze</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Fonte Corsair CX650 650W 80 Plus Bronze</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Fonte de alimentação ATX CORSAIR 650W - CX650 80 PLUS Bronze</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>379.99</v>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0D1LVW7T6</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0D1LVW7T6</t>
+          <t>Fonte de alimentação ATX CORSAIR 650W - CX650 80 PLUS Bronze</t>
         </is>
       </c>
     </row>
@@ -2096,30 +2332,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Fonte MSI MAG A650BN 650W 80 Plus Bronze</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Fonte MSI MAG A650BN 650W 80 Plus Bronze</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Fonte de Alimentação MSI MAG A650BN, 650W, 80 Plus Bronze, PFC Ativo, Com Cabo, Preto - MAGA650BNL</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>279.99</v>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0CXQDHYZL</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0CXQDHYZL</t>
+          <t>Fonte de Alimentação MSI MAG A650BN, 650W, 80 Plus Bronze, PFC Ativo, Com Cabo, Preto - MAGA650BNL</t>
         </is>
       </c>
     </row>
@@ -2129,34 +2370,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 5600</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 5600, 3.5GHz (4.4GHz Turbo), AM4 - 100-100000927BOX</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>827.9</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/355263/processador-amd-ryzen-5-5600-3-5ghz-4-4ghz-turbo-am4-100-100000927box</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 5600, 3.5GHz (4.4GHz Turbo), AM4 - 100-100000927BOX</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
         <v>919.89</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/355263/processador-amd-ryzen-5-5600-3-5ghz-4-4ghz-turbo-am4-100-100000927box</t>
-        </is>
       </c>
     </row>
     <row r="50">
@@ -2165,34 +2411,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 5700X</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 5700X</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 5700X, 3.4GHz (4.6GHz Max Turbo), Cache 36MB, 8 Núcleos, 16 Threads, AM4, Sem Vídeo Integrado - 100-100000926WOF</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1199.99</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/320797/processador-amd-ryzen-7-5700x-3-4ghz-4-6ghz-max-turbo-cache-36mb-8-nucleos-16-threads-am4-sem-video-integrado-100-100000926wof</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 5700X, 3.4GHz (4.6GHz Max Turbo), Cache 36MB, 8 Núcleos, 16 Threads, AM4, Sem Vídeo Integrado - 100-100000926WOF</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
         <v>2686.16</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/320797/processador-amd-ryzen-7-5700x-3-4ghz-4-6ghz-max-turbo-cache-36mb-8-nucleos-16-threads-am4-sem-video-integrado-100-100000926wof</t>
-        </is>
       </c>
     </row>
     <row r="51">
@@ -2201,34 +2452,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 7600</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 7600, 3.8GHz (5.1GHz Max Turbo), Cache 38MB, 6 Núcleos, 12 Threads, AM5, Com Vídeo Integrado - 100-100001015BOX</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>999.99</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/405799/processador-amd-ryzen-5-7600-3-8ghz-5-1ghz-max-turbo-cache-38mb-6-nucleos-12-threads-am5-com-video-integrado-100-100001015box</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 7600, 3.8GHz (5.1GHz Max Turbo), Cache 38MB, 6 Núcleos, 12 Threads, AM5, Com Vídeo Integrado - 100-100001015BOX</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
         <v>1823.52</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/405799/processador-amd-ryzen-5-7600-3-8ghz-5-1ghz-max-turbo-cache-38mb-6-nucleos-12-threads-am5-com-video-integrado-100-100001015box</t>
-        </is>
       </c>
     </row>
     <row r="52">
@@ -2237,34 +2493,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 7800X3D</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 7800x3d, 4.2GHz, 5.0GHz Max Turbo, Cache 104MB, Am5, C/ Vídeo E Sem Cooler - 100-100000910wof</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1978.9</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/466557/processador-amd-ryzen-7-7800x3d-4-2ghz-5-0ghz-max-turbo-cache-104mb-am5-c-video-e-sem-cooler-100-100000910wof</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 7800x3d, 4.2GHz, 5.0GHz Max Turbo, Cache 104MB, Am5, C/ Vídeo E Sem Cooler - 100-100000910wof</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
         <v>2264.19</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/466557/processador-amd-ryzen-7-7800x3d-4-2ghz-5-0ghz-max-turbo-cache-104mb-am5-c-video-e-sem-cooler-100-100000910wof</t>
-        </is>
       </c>
     </row>
     <row r="53">
@@ -2273,34 +2534,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-12400F</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-12400F, 2.5GHz (4.4GHz Max Turbo), Cache 18MB, 6 Núcleos, 12 Threads, LGA 1700, Sem Vídeo Integrado - BX8071512400F</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>899.99</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/283718/processador-intel-core-i5-12400f-2-5ghz-4-4ghz-max-turbo-cache-18mb-6-nucleos-12-threads-lga-1700-sem-video-integrado-bx8071512400f</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-12400F, 2.5GHz (4.4GHz Max Turbo), Cache 18MB, 6 Núcleos, 12 Threads, LGA 1700, Sem Vídeo Integrado - BX8071512400F</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
         <v>1658.32</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/283718/processador-intel-core-i5-12400f-2-5ghz-4-4ghz-max-turbo-cache-18mb-6-nucleos-12-threads-lga-1700-sem-video-integrado-bx8071512400f</t>
-        </is>
       </c>
     </row>
     <row r="54">
@@ -2309,34 +2575,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-14400F</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Processador Intel Core I5 14400f 14ª Geração, 3.5 Ghz (4.7 Ghz Turbo), Cache 20mb, 10 Núcleos, 16 Threads, Lga1700, S/ Vídeo Integrado - Bx8071514400f</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1069.99</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/531209/processador-intel-core-i5-14400f-14-geracao-3-5-ghz-4-7-ghz-turbo-cache-20mb-10-nucleos-16-threads-lga1700-sem-video-integrado-bx8071514400f</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Processador Intel Core I5 14400f 14ª Geração, 3.5 Ghz (4.7 Ghz Turbo), Cache 20mb, 10 Núcleos, 16 Threads, Lga1700, S/ Vídeo Integrado - Bx8071514400f</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
         <v>1189.99</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/531209/processador-intel-core-i5-14400f-14-geracao-3-5-ghz-4-7-ghz-turbo-cache-20mb-10-nucleos-16-threads-lga1700-sem-video-integrado-bx8071514400f</t>
-        </is>
       </c>
     </row>
     <row r="55">
@@ -2345,34 +2616,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 5060 8GB</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 5060 8GB</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Placa de Video Palit GeForce RTX 5060 8GB INFINITY 2 OC GDDR7 128bits - NE75060V19P1-GB2063L</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>2799.99</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/988706/placa-de-video-palit-geforce-rtx-5060-8gb-infinity-2-oc-gddr7-128bits-ne75060v19p1-gb2063l</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Placa de Video Palit GeForce RTX 5060 8GB INFINITY 2 OC GDDR7 128bits - NE75060V19P1-GB2063L</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
         <v>3823.98</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/988706/placa-de-video-palit-geforce-rtx-5060-8gb-infinity-2-oc-gddr7-128bits-ne75060v19p1-gb2063l</t>
-        </is>
       </c>
     </row>
     <row r="56">
@@ -2381,34 +2657,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 5070 12GB</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 5070 12GB</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Placa de Video Palit GeForce RTX 5070 WHITE OC 12GB GDDR7 192bit 3-DP e HDMI - NE75070U19K9-GB2050W</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>5299.99</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/989622/placa-de-video-palit-geforce-rtx-5070-white-oc-12gb-gddr7-192bit-3-dp-e-hdmi-ne75070u19k9-gb2050w</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Placa de Video Palit GeForce RTX 5070 WHITE OC 12GB GDDR7 192bit 3-DP e HDMI - NE75070U19K9-GB2050W</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
         <v>6666.66</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/989622/placa-de-video-palit-geforce-rtx-5070-white-oc-12gb-gddr7-192bit-3-dp-e-hdmi-ne75070u19k9-gb2050w</t>
-        </is>
       </c>
     </row>
     <row r="57">
@@ -2417,34 +2698,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 3060 12GB</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 3060 12GB</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Placa De Vídeo Husky Alpha RTX 3060, Nvidia, 12GB, GDDR6, 192-Bit, Dual Fan, HDMI, 3x DisplayPort - HVG023060</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>2199.99</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/996572/placa-de-video-husky-alpha-rtx-3060-nvidia-12gb-gddr6-192-bit-dual-fan-hdmi-3x-displayport-hvg023060</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Placa De Vídeo Husky Alpha RTX 3060, Nvidia, 12GB, GDDR6, 192-Bit, Dual Fan, HDMI, 3x DisplayPort - HVG023060</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
         <v>3529.4</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/996572/placa-de-video-husky-alpha-rtx-3060-nvidia-12gb-gddr6-192-bit-dual-fan-hdmi-3x-displayport-hvg023060</t>
-        </is>
       </c>
     </row>
     <row r="58">
@@ -2453,34 +2739,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo Radeon RX 7600 8GB</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo Radeon RX 7600 8GB</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo RX 7600 Challenger ASRock AMD Radeon,  8GB GDDR6 - 90-GA41ZZ-00UANF</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1909.99</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/459144/placa-de-video-rx-7600-challenger-asrock-amd-radeon-8gb-gddr6-90-ga41zz-00uanf</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo RX 7600 Challenger ASRock AMD Radeon,  8GB GDDR6 - 90-GA41ZZ-00UANF</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
         <v>2823.52</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/459144/placa-de-video-rx-7600-challenger-asrock-amd-radeon-8gb-gddr6-90-ga41zz-00uanf</t>
-        </is>
       </c>
     </row>
     <row r="59">
@@ -2489,34 +2780,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 8GB DDR4 3200MHz</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 8GB DDR4 3200MHz</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Memória RAM Kingston Fury Beast, 8GB, 3200MHz, DDR4, CL16, Preto - KF432C16BB/8</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>669.99</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/172365/memoria-ram-kingston-fury-beast-8gb-3200mhz-ddr4-cl16-preto-kf432c16bb-8</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Memória RAM Kingston Fury Beast, 8GB, 3200MHz, DDR4, CL16, Preto - KF432C16BB/8</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
         <v>952.74</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/172365/memoria-ram-kingston-fury-beast-8gb-3200mhz-ddr4-cl16-preto-kf432c16bb-8</t>
-        </is>
       </c>
     </row>
     <row r="60">
@@ -2525,34 +2821,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 16GB DDR4 3200MHz</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 16GB DDR4 3200MHz</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Memória Ram Kingston Hyperx Fury Beast Ddr4 16gb 3200mhz Cl16 Udimm – Desktop</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>999.3099999999999</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/938663/memoria-ram-kingston-hyperx-ddr4-16gb-2666mhz-cl16-udimm-desktop</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Memória Ram Kingston Hyperx Fury Beast Ddr4 16gb 3200mhz Cl16 Udimm – Desktop</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
         <v>1051.9</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/938663/memoria-ram-kingston-hyperx-ddr4-16gb-2666mhz-cl16-udimm-desktop</t>
-        </is>
       </c>
     </row>
     <row r="61">
@@ -2561,34 +2862,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast, 16GB, 5600MHz, DDR5, CL40, Preto - KF556C40BB-16</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>2199</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/349654/memoria-kingston-fury-beast-16gb-5600mhz-ddr5-cl40-preto-kf556c40bb-16</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast, 16GB, 5600MHz, DDR5, CL40, Preto - KF556C40BB-16</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
         <v>2199</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/349654/memoria-kingston-fury-beast-16gb-5600mhz-ddr5-cl40-preto-kf556c40bb-16</t>
-        </is>
       </c>
     </row>
     <row r="62">
@@ -2597,34 +2903,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SSD Kingston NV3 1TB M.2 NVMe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>SSD Kingston NV3 1TB M.2 NVMe</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>SSD Kingston 1TB Nv3 M.2 Nvme PCIe 4, Leitura 6000MB/s, Gravação 4000MB/s, Ultra Rápido - Snv3s/1000g</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1032.13</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/633107/ssd-kingston-1tb-padrao-nv3-m-2-2280-nvme-4-0-gen-4x4-leitura-6000-e-gravacao-4000mbps-ultra-rapido-snv3s-1000g</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>SSD Kingston 1TB Nv3 M.2 Nvme PCIe 4, Leitura 6000MB/s, Gravação 4000MB/s, Ultra Rápido - Snv3s/1000g</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
         <v>1146.81</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/633107/ssd-kingston-1tb-padrao-nv3-m-2-2280-nvme-4-0-gen-4x4-leitura-6000-e-gravacao-4000mbps-ultra-rapido-snv3s-1000g</t>
-        </is>
       </c>
     </row>
     <row r="63">
@@ -2633,34 +2944,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SSD Samsung 990 Pro 1TB M.2 NVMe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>SSD Samsung 990 Pro 1TB M.2 NVMe</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>SSD Samsung 990 Pro 1TB, Nvme M.2 2280, Mz-v9p1t0b/am.</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>2399</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/464267/ssd-samsung-990-pro-1tb-nvme-m-2-2280-mz-v9p1t0b-am-</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>SSD Samsung 990 Pro 1TB, Nvme M.2 2280, Mz-v9p1t0b/am.</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
         <v>2399</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/464267/ssd-samsung-990-pro-1tb-nvme-m-2-2280-mz-v9p1t0b-am-</t>
-        </is>
       </c>
     </row>
     <row r="64">
@@ -2669,34 +2985,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SSD Kingston A400 480GB SATA</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>SSD Kingston A400 480GB SATA</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>SSD Kingston A400, 480GB, Sata Iii, 2.5", Leitura: 500mb/s, Gravação: 450mb/s, Preto - Sa400s37/480g</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>466.39</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/781777/ssd-kingston-a400-480gb-sata-iii-2-5-leitura-500mb-s-gravacao-450mb-s-preto-sa400s37-480g</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>SSD Kingston A400, 480GB, Sata Iii, 2.5", Leitura: 500mb/s, Gravação: 450mb/s, Preto - Sa400s37/480g</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
         <v>529.99</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/781777/ssd-kingston-a400-480gb-sata-iii-2-5-leitura-500mb-s-gravacao-450mb-s-preto-sa400s37-480g</t>
-        </is>
       </c>
     </row>
     <row r="65">
@@ -2705,34 +3026,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Placa-mãe ASUS TUF Gaming B550M-Plus</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>Placa-mãe</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Placa-mãe ASUS TUF Gaming B550M-Plus</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Placa-Mãe Asus TUF Gaming B550M-PLUS, AMD AM4, mATX , DDR4, M.2, Aura para fita RGB - 90MB14A0-C1BAY0</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>741.9</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/172706/placa-mae-asus-tuf-gaming-b550m-plus-amd-am4-matx-ddr4-m-2-aura-para-fita-rgb-90mb14a0-c1bay0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Placa-Mãe Asus TUF Gaming B550M-PLUS, AMD AM4, mATX , DDR4, M.2, Aura para fita RGB - 90MB14A0-C1BAY0</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
         <v>824.33</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/172706/placa-mae-asus-tuf-gaming-b550m-plus-amd-am4-matx-ddr4-m-2-aura-para-fita-rgb-90mb14a0-c1bay0</t>
-        </is>
       </c>
     </row>
     <row r="66">
@@ -2741,34 +3067,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Placa-mãe MSI PRO B650M-P</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>Placa-mãe</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Placa-mãe MSI PRO B650M-P</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Placa Mãe Msi Pro B650m-p, Matx Am5 Ddr5 HDMI, Displayport Vga M.2 Usb 3.2</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>994.38</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/532385/placa-mae-msi-pro-b650m-p-matx-am5-ddr5-hdmi-displayport-vga-m-2-usb-3-2</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Placa Mãe Msi Pro B650m-p, Matx Am5 Ddr5 HDMI, Displayport Vga M.2 Usb 3.2</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
         <v>1057.85</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/532385/placa-mae-msi-pro-b650m-p-matx-am5-ddr5-hdmi-displayport-vga-m-2-usb-3-2</t>
-        </is>
       </c>
     </row>
     <row r="67">
@@ -2777,34 +3108,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Fonte Corsair CX650 650W 80 Plus Bronze</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Fonte Corsair CX650 650W 80 Plus Bronze</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Fonte Corsair CX Series CX650, 650W, 80 Plus Bronze, Com Cabo, Preto - CP-9020278-BR</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>359.99</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/516056/fonte-corsair-cx-series-cx650-650w-80-plus-bronze-com-cabo-preto-cp-9020278-br</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Fonte Corsair CX Series CX650, 650W, 80 Plus Bronze, Com Cabo, Preto - CP-9020278-BR</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
         <v>433.32</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/516056/fonte-corsair-cx-series-cx650-650w-80-plus-bronze-com-cabo-preto-cp-9020278-br</t>
-        </is>
       </c>
     </row>
     <row r="68">
@@ -2813,34 +3149,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Fonte MSI MAG A650BN 650W 80 Plus Bronze</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Fonte MSI MAG A650BN 650W 80 Plus Bronze</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Fonte MSI MAG A650BN, 650W, 80 Plus Bronze, PFC Ativo, Com Cabo, Preto - 306-7ZP2B22-CE0</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>289.99</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/369658/fonte-msi-mag-a650bn-650w-80-plus-bronze-pfc-ativo-com-cabo-preto-306-7zp2b22-ce0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Fonte MSI MAG A650BN, 650W, 80 Plus Bronze, PFC Ativo, Com Cabo, Preto - 306-7ZP2B22-CE0</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
         <v>388.88</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/369658/fonte-msi-mag-a650bn-650w-80-plus-bronze-pfc-ativo-com-cabo-preto-306-7zp2b22-ce0</t>
-        </is>
       </c>
     </row>
     <row r="69">
@@ -2849,34 +3190,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Fonte XPG Core Reactor II VE 750W 80 Plus Gold</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Fonte XPG Core Reactor II VE 750W 80 Plus Gold</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Fonte Xpg Core Reactor Ii Ve, 750w, 80 Plus Gold, Modular, Pfc Ativo, Preta - 75261425</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>753.95</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/1074346/fonte-xpg-core-reactor-ii-ve-750w-80-plus-gold-modular-pfc-ativo-preta-75261425</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Fonte Xpg Core Reactor Ii Ve, 750w, 80 Plus Gold, Modular, Pfc Ativo, Preta - 75261425</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
         <v>793.63</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/1074346/fonte-xpg-core-reactor-ii-ve-750w-80-plus-gold-modular-pfc-ativo-preta-75261425</t>
-        </is>
       </c>
     </row>
     <row r="70">
@@ -2885,34 +3231,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>pichau</t>
+          <t>Pichau</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>https://www.pichau.com.br</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo Radeon RX 7600 8GB</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo Radeon RX 7600 8GB</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Placa de Video AsRock Radeon RX 7600 Challenger Pro OC, 8GB, GDDR6, 128-bit, 90-GA62ZZ-00UANF</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>2199.99</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.pichau.com.br/placa-de-video-asrock-radeon-rx-7600-challenger-pro-oc-8gb-gddr6-128-bit-90-ga62zz-00uanf</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Placa de Video AsRock Radeon RX 7600 Challenger Pro OC, 8GB, GDDR6, 128-bit, 90-GA62ZZ-00UANF</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
         <v>2588.22</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>https://www.pichau.com.br/placa-de-video-asrock-radeon-rx-7600-challenger-pro-oc-8gb-gddr6-128-bit-90-ga62zz-00uanf</t>
-        </is>
       </c>
     </row>
     <row r="71">
@@ -2921,34 +3272,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>terabyte</t>
+          <t>Terabyte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>https://www.terabyteshop.com.br</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 5060 8GB</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 5060 8GB</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo PCYES NVIDIA GeForce RTX 5060, 8GB, GDDR7, DLSS, Ray Tracing, PVRTX5060B2F128</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>2699.99</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/43432/placa-de-video-pcyes-nvidia-geforce-rtx-5060-8gb-gddr7-128bits-dual-fan-pvrtx5060b2f128</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo PCYES NVIDIA GeForce RTX 5060, 8GB, GDDR7, DLSS, Ray Tracing, PVRTX5060B2F128</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
         <v>3176.52</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>https://www.terabyteshop.com.br/produto/43432/placa-de-video-pcyes-nvidia-geforce-rtx-5060-8gb-gddr7-128bits-dual-fan-pvrtx5060b2f128</t>
-        </is>
       </c>
     </row>
     <row r="72">
@@ -2957,34 +3313,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>terabyte</t>
+          <t>Terabyte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>https://www.terabyteshop.com.br</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 5070 12GB</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 5070 12GB</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo Asus NVIDIA GeForce RTX 5070 ATS OC V2, 12GB, GDDR7, DLSS, Ray Tracing, ATS-RTX5070-O12G-V2</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>5599.99</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/43330/placa-de-video-asus-nvidia-geforce-rtx-5070-ats-oc-v2-12gb-gddr7-dlss-ray-tracing-ats-rtx5070-o12g-v2</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo Asus NVIDIA GeForce RTX 5070 ATS OC V2, 12GB, GDDR7, DLSS, Ray Tracing, ATS-RTX5070-O12G-V2</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
         <v>6588.24</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>https://www.terabyteshop.com.br/produto/43330/placa-de-video-asus-nvidia-geforce-rtx-5070-ats-oc-v2-12gb-gddr7-dlss-ray-tracing-ats-rtx5070-o12g-v2</t>
-        </is>
       </c>
     </row>
     <row r="73">
@@ -2993,34 +3354,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>terabyte</t>
+          <t>Terabyte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>https://www.terabyteshop.com.br</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 3060 12GB</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 3060 12GB</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo SuperFrame NVIDIA GeForce RTX 3060 EPIC Especial Edition, White, 12GB, GDDR6, DLSS, Ray Tracing, SF-GC-EPNV306012GD6</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>2589.99</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/36876/placa-de-video-superframe-nvidia-geforce-rtx-3060-epic-especial-edition-white-12gb-gddr6-dlss-ray-tracing-sf-gc-spnv306012d6</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo SuperFrame NVIDIA GeForce RTX 3060 EPIC Especial Edition, White, 12GB, GDDR6, DLSS, Ray Tracing, SF-GC-EPNV306012GD6</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
         <v>3047.04</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>https://www.terabyteshop.com.br/produto/36876/placa-de-video-superframe-nvidia-geforce-rtx-3060-epic-especial-edition-white-12gb-gddr6-dlss-ray-tracing-sf-gc-spnv306012d6</t>
-        </is>
       </c>
     </row>
     <row r="74">
@@ -3029,30 +3395,35 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 5600</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 5600 AM4 3.5GHz (Sem caixa) – 6 Núcleos 12 Threads – Até 4.4GHz – NoBox</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>835.9</v>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0GKHVP14D</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0GKHVP14D</t>
+          <t>Processador AMD Ryzen 5 5600 AM4 3.5GHz (Sem caixa) – 6 Núcleos 12 Threads – Até 4.4GHz – NoBox</t>
         </is>
       </c>
     </row>
@@ -3062,30 +3433,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 5700X</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 5700X</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 5700X, 3,4 GHz, 8 núcleos, 16 threads, cache de 32 MB, soquete AM4, OEM</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>987.05</v>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0C3T4MFMM</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0C3T4MFMM</t>
+          <t>Processador AMD Ryzen 7 5700X, 3,4 GHz, 8 núcleos, 16 threads, cache de 32 MB, soquete AM4, OEM</t>
         </is>
       </c>
     </row>
@@ -3095,30 +3471,35 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 7600</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>PROCESSADOR AMD RYZEN 5 7600 4.0GHz (TURBO 5.2GHz) 38MB CACHE AM5 100-100001015BOX</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>999.99</v>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0BMQJWBDM</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0BMQJWBDM</t>
+          <t>PROCESSADOR AMD RYZEN 5 7600 4.0GHz (TURBO 5.2GHz) 38MB CACHE AM5 100-100001015BOX</t>
         </is>
       </c>
     </row>
@@ -3128,30 +3509,35 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 7800X3D</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AMD Ryzen 7 7800X3D 8 x 4,2GHz Octa Core Processador (CPU) Bandeja Socket (PC): AM5 120W</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>1895.89</v>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0CTD76W9C</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0CTD76W9C</t>
+          <t>AMD Ryzen 7 7800X3D 8 x 4,2GHz Octa Core Processador (CPU) Bandeja Socket (PC): AM5 120W</t>
         </is>
       </c>
     </row>
@@ -3161,30 +3547,35 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-12400F</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>PROCESSADOR INTEL CORE I5-12400F 2.5GHz (TURBO 4.4GHz) 18MB CACHE LGA1700 12° GERACAO BX8071512400F</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>1105.17</v>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B09NPJRDGD</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B09NPJRDGD</t>
+          <t>PROCESSADOR INTEL CORE I5-12400F 2.5GHz (TURBO 4.4GHz) 18MB CACHE LGA1700 12° GERACAO BX8071512400F</t>
         </is>
       </c>
     </row>
@@ -3194,30 +3585,35 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-14400F</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-14400F LGA 1700 BX8071514400F</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1000</v>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0CQ3142LB</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0CQ3142LB</t>
+          <t>Processador Intel Core i5-14400F LGA 1700 BX8071514400F</t>
         </is>
       </c>
     </row>
@@ -3227,30 +3623,35 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 5060 8GB</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 5060 8GB</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>GAINWARD Placa gráfica RTX 5060 Ghost 8GB GDDR7 128bit 3-DP HDMI NE75060019P1-GB2063B VD9198</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>2799.98</v>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0F8H4RWB8</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0F8H4RWB8</t>
+          <t>GAINWARD Placa gráfica RTX 5060 Ghost 8GB GDDR7 128bit 3-DP HDMI NE75060019P1-GB2063B VD9198</t>
         </is>
       </c>
     </row>
@@ -3260,30 +3661,35 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 5070 12GB</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 5070 12GB</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Palit RTX5070 Branco OC 12GB GDDR7 NE75070U19K9-GB2050W Retail</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>5594.43</v>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0FQV7G9WY</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0FQV7G9WY</t>
+          <t>Palit RTX5070 Branco OC 12GB GDDR7 NE75070U19K9-GB2050W Retail</t>
         </is>
       </c>
     </row>
@@ -3293,30 +3699,35 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 3060 12GB</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 3060 12GB</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Placa De Vídeo Husky Alpha RTX 3060, Nvidia, 12GB, GDDR6, 192-Bit, Dual Fan, HDMI, 3x DisplayPort - HVG023060</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>2458.8</v>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0H378SSY3</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0H378SSY3</t>
+          <t>Placa De Vídeo Husky Alpha RTX 3060, Nvidia, 12GB, GDDR6, 192-Bit, Dual Fan, HDMI, 3x DisplayPort - HVG023060</t>
         </is>
       </c>
     </row>
@@ -3326,30 +3737,35 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo Radeon RX 7600 8GB</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo Radeon RX 7600 8GB</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo ASRock Radeon RX 7600 Challenger OC, 8GB, GDDR6, 128-Bit, FSR, Ray Tracing, Preto</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>2134.69</v>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0C626FFG2</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0C626FFG2</t>
+          <t>Placa de Vídeo ASRock Radeon RX 7600 Challenger OC, 8GB, GDDR6, 128-Bit, FSR, Ray Tracing, Preto</t>
         </is>
       </c>
     </row>
@@ -3359,30 +3775,35 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 8GB DDR4 3200MHz</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 8GB DDR4 3200MHz</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>MEMÓRIA KINGSTON FURY BEAST DIMM DDR4 8GB 3200 MHZ KF432C16BB/8 1,35V 1Rx* 288 pinos Desktop Gamer</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>451.24</v>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B097K5J1SB</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B097K5J1SB</t>
+          <t>MEMÓRIA KINGSTON FURY BEAST DIMM DDR4 8GB 3200 MHZ KF432C16BB/8 1,35V 1Rx* 288 pinos Desktop Gamer</t>
         </is>
       </c>
     </row>
@@ -3392,30 +3813,35 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 16GB DDR4 3200MHz</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 16GB DDR4 3200MHz</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>KF432C16BB/16 - Memória de 16GB DIMM DDR4 3200Mhz FURY Beast 1,35V 1Rx8 288 pinos para desktop/gamers, Preto</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>798.1900000000001</v>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B097K3WV9J</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B097K3WV9J</t>
+          <t>KF432C16BB/16 - Memória de 16GB DIMM DDR4 3200Mhz FURY Beast 1,35V 1Rx8 288 pinos para desktop/gamers, Preto</t>
         </is>
       </c>
     </row>
@@ -3425,30 +3851,35 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Kingston KF556C40BB-16 - Módulo de memória de 16GB DDR5 5600Mhz FURY Beast Black 1,25V 1Rx8 288 pinos para desktop/gamers,NULL</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>2070.99</v>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B09N5WSSQD</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B09N5WSSQD</t>
+          <t>Kingston KF556C40BB-16 - Módulo de memória de 16GB DDR5 5600Mhz FURY Beast Black 1,25V 1Rx8 288 pinos para desktop/gamers,NULL</t>
         </is>
       </c>
     </row>
@@ -3458,30 +3889,35 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>SSD Kingston NV3 1TB M.2 NVMe</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>SSD Kingston NV3 1TB M.2 NVMe</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>SSD Kingston NV3 1TB M.2 2280 NVMe Gen4, Desempenho e Eficiência para Upgrade de PC – SNV3S/1000G</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>930.05</v>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0DBR3DZWG</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0DBR3DZWG</t>
+          <t>SSD Kingston NV3 1TB M.2 2280 NVMe Gen4, Desempenho e Eficiência para Upgrade de PC – SNV3S/1000G</t>
         </is>
       </c>
     </row>
@@ -3491,30 +3927,35 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SSD Samsung 990 Pro 1TB M.2 NVMe</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>SSD Samsung 990 Pro 1TB M.2 NVMe</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>SSD Samsung 990 PRO 1TB NVMe M.2 2280 (Leitura até 7450MB/s e Gravação até 6900MB/s)</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>1702.98</v>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0BHJF2VRN</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0BHJF2VRN</t>
+          <t>SSD Samsung 990 PRO 1TB NVMe M.2 2280 (Leitura até 7450MB/s e Gravação até 6900MB/s)</t>
         </is>
       </c>
     </row>
@@ -3524,30 +3965,35 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SSD Kingston A400 480GB SATA</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>SSD Kingston A400 480GB SATA</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Ssd 480Gb Kingston A400 Bulk</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>615.6</v>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B08NG86HZD</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B08NG86HZD</t>
+          <t>Ssd 480Gb Kingston A400 Bulk</t>
         </is>
       </c>
     </row>
@@ -3557,30 +4003,35 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Placa-mãe MSI PRO B650M-P</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>Placa-mãe</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Placa-mãe MSI PRO B650M-P</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>MSI Placa-mãe PRO B650M-P V1, Micro-ATX - Suporta processadores AMD Ryzen 9000/8000/7000, AM5 - DDR5 Memory Boost 6000+MHz/OC, 1 x PCIe 4.0 x16, 2 x M.2 Gen4, LAN 2.5G</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>1371.19</v>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0FBT23ZY8</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0FBT23ZY8</t>
+          <t>MSI Placa-mãe PRO B650M-P V1, Micro-ATX - Suporta processadores AMD Ryzen 9000/8000/7000, AM5 - DDR5 Memory Boost 6000+MHz/OC, 1 x PCIe 4.0 x16, 2 x M.2 Gen4, LAN 2.5G</t>
         </is>
       </c>
     </row>
@@ -3590,30 +4041,35 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Fonte Corsair CX650 650W 80 Plus Bronze</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Fonte Corsair CX650 650W 80 Plus Bronze</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Fonte de alimentação ATX CORSAIR 650W - CX650 80 PLUS Bronze</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>379.99</v>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0D1LVW7T6</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0D1LVW7T6</t>
+          <t>Fonte de alimentação ATX CORSAIR 650W - CX650 80 PLUS Bronze</t>
         </is>
       </c>
     </row>
@@ -3623,30 +4079,35 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.br</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Fonte MSI MAG A650BN 650W 80 Plus Bronze</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Fonte MSI MAG A650BN 650W 80 Plus Bronze</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Fonte de Alimentação MSI MAG A650BN, 650W, 80 Plus Bronze, PFC Ativo, Com Cabo, Preto - MAGA650BNL</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>279.99</v>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0CXQDHYZL</t>
+        </is>
+      </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/dp/B0CXQDHYZL</t>
+          <t>Fonte de Alimentação MSI MAG A650BN, 650W, 80 Plus Bronze, PFC Ativo, Com Cabo, Preto - MAGA650BNL</t>
         </is>
       </c>
     </row>
@@ -3656,34 +4117,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>terabyte</t>
+          <t>Terabyte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
+          <t>https://www.terabyteshop.com.br</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 8GB DDR4 3200MHz</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 8GB DDR4 3200MHz</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Memória DDR4 Kingston Fury Beast, 8GB, 3200MHz, Black, KF432C16BB/8</t>
         </is>
       </c>
       <c r="F93" t="n">
         <v>699.9</v>
       </c>
-      <c r="G93" t="n">
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/19314/memoria-kingston-fury-beast-8gb-3200mhz-ddr4-black-kf432c16bb8</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Memória DDR4 Kingston Fury Beast, 8GB, 3200MHz, Black, KF432C16BB/8</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
         <v>823.4400000000001</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>https://www.terabyteshop.com.br/produto/19314/memoria-kingston-fury-beast-8gb-3200mhz-ddr4-black-kf432c16bb8</t>
-        </is>
       </c>
     </row>
     <row r="94">
@@ -3692,34 +4158,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>terabyte</t>
+          <t>Terabyte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
+          <t>https://www.terabyteshop.com.br</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 16GB DDR4 3200MHz</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 16GB DDR4 3200MHz</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Memória DDR4 Kingston Fury Beast, 16GB, 3200MHz, Preto, KF432C16BB/16</t>
         </is>
       </c>
       <c r="F94" t="n">
         <v>1859.9</v>
       </c>
-      <c r="G94" t="n">
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/21175/memoria-kingston-fury-beast-16gb-3200mhz-ddr4-preto-kf432c16bb16</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Memória DDR4 Kingston Fury Beast, 16GB, 3200MHz, Preto, KF432C16BB/16</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
         <v>2188.08</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>https://www.terabyteshop.com.br/produto/21175/memoria-kingston-fury-beast-16gb-3200mhz-ddr4-preto-kf432c16bb16</t>
-        </is>
       </c>
     </row>
     <row r="95">
@@ -3728,38 +4199,43 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>terabyte</t>
+          <t>Terabyte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>https://www.terabyteshop.com.br</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Memória DDR5 Kingston FURY Beast, 16GB, 5600MHz, Black, KF556C40BB-16</t>
         </is>
       </c>
       <c r="F95" t="n">
         <v>2529.9</v>
       </c>
-      <c r="G95" t="n">
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/20394/memoria-ddr5-kingston-fury-beast-16gb-5600mhz-black-kf556c40bb-16</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Memória DDR5 Kingston FURY Beast, 16GB, 5600MHz, Black, KF556C40BB-16</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
         <v>2976.36</v>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>https://www.terabyteshop.com.br/produto/20394/memoria-ddr5-kingston-fury-beast-16gb-5600mhz-black-kf556c40bb-16</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H95"/>
+  <autoFilter ref="A1:I95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>